--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/inesappelquist/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_66F04BC88F2E741A019C2044AE45E5A75D9700FE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C77F12B6-209E-2A4E-835F-DCD064A103B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17240" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17240" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="P6b" sheetId="11" r:id="rId11"/>
     <sheet name="P6c" sheetId="12" r:id="rId12"/>
     <sheet name="P6d" sheetId="13" r:id="rId13"/>
+    <sheet name="Graphs" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="78">
   <si>
     <t>Training Log Summary — Run 2 Only</t>
   </si>
@@ -244,15 +245,52 @@
   <si>
     <t>Part 6d: Global Average Pooling (Replacing FC Layer)</t>
   </si>
+  <si>
+    <t>Graphs for CIFAR-10 ConvNet experiments</t>
+  </si>
+  <si>
+    <t>Final model selected by best validation accuracy: P6b — LR Scheduler (Cosine Annealing with Warm Restarts) (90.4%).</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Raw VGG</t>
+  </si>
+  <si>
+    <t>Dropout</t>
+  </si>
+  <si>
+    <t>Weight decay</t>
+  </si>
+  <si>
+    <t>Augmentation</t>
+  </si>
+  <si>
+    <t>Combined</t>
+  </si>
+  <si>
+    <t>Advanced augmentation</t>
+  </si>
+  <si>
+    <t>Downsampling</t>
+  </si>
+  <si>
+    <t>Global average pooling</t>
+  </si>
+  <si>
+    <t>Learning-rate scheduler</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -281,8 +319,19 @@
       <color rgb="FF1F4E78"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -309,6 +358,21 @@
         <fgColor rgb="FFD9EAF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0B1F33"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -322,7 +386,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -342,11 +406,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -472,7 +546,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-CFC5-BD4F-9522-542EDEF34020}"/>
+              <c16:uniqueId val="{00000000-0ABC-964B-A36E-0CB49CDA4113}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -568,7 +642,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-CFC5-BD4F-9522-542EDEF34020}"/>
+              <c16:uniqueId val="{00000001-0ABC-964B-A36E-0CB49CDA4113}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -852,7 +926,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-963D-E64D-812E-F251CAC173D1}"/>
+              <c16:uniqueId val="{00000000-E914-544B-B7A2-7250B642107F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1033,7 +1107,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-963D-E64D-812E-F251CAC173D1}"/>
+              <c16:uniqueId val="{00000001-E914-544B-B7A2-7250B642107F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1318,7 +1392,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C296-F140-93D9-7C773560146D}"/>
+              <c16:uniqueId val="{00000000-76BF-E64D-A2D1-AECBE04DCAFF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1499,7 +1573,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-C296-F140-93D9-7C773560146D}"/>
+              <c16:uniqueId val="{00000001-76BF-E64D-A2D1-AECBE04DCAFF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1784,7 +1858,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-75DB-064B-9479-24179B3EA122}"/>
+              <c16:uniqueId val="{00000000-1AD4-0B4D-B6CA-8B02DF3B8D67}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1965,7 +2039,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-75DB-064B-9479-24179B3EA122}"/>
+              <c16:uniqueId val="{00000001-1AD4-0B4D-B6CA-8B02DF3B8D67}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2250,7 +2324,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-98DF-8B44-AC6A-9897CD6725F4}"/>
+              <c16:uniqueId val="{00000000-7DCD-FB4E-B41F-9D1AC749486D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2431,7 +2505,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-98DF-8B44-AC6A-9897CD6725F4}"/>
+              <c16:uniqueId val="{00000001-7DCD-FB4E-B41F-9D1AC749486D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2866,7 +2940,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-AD62-A741-97CF-B8ADF45DD3F8}"/>
+              <c16:uniqueId val="{00000000-F34B-2B4F-AA0E-A0DB703DC1DD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3197,7 +3271,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-AD62-A741-97CF-B8ADF45DD3F8}"/>
+              <c16:uniqueId val="{00000001-F34B-2B4F-AA0E-A0DB703DC1DD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3632,7 +3706,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-90A6-F34F-9E53-92079313B38C}"/>
+              <c16:uniqueId val="{00000000-73F3-A547-BB02-B647B57FC25B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3963,7 +4037,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-90A6-F34F-9E53-92079313B38C}"/>
+              <c16:uniqueId val="{00000001-73F3-A547-BB02-B647B57FC25B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4398,7 +4472,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-10C6-EA4D-82F4-E6F7DC1C6EF3}"/>
+              <c16:uniqueId val="{00000000-B148-2241-847B-89A22EEDE657}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4729,7 +4803,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-10C6-EA4D-82F4-E6F7DC1C6EF3}"/>
+              <c16:uniqueId val="{00000001-B148-2241-847B-89A22EEDE657}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5164,7 +5238,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-82BA-0D49-85E3-BA43A345F2E9}"/>
+              <c16:uniqueId val="{00000000-FFA2-5940-AB1B-7C9BB1682B89}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5495,7 +5569,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-82BA-0D49-85E3-BA43A345F2E9}"/>
+              <c16:uniqueId val="{00000001-FFA2-5940-AB1B-7C9BB1682B89}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5930,7 +6004,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7283-5249-A40E-10B6D9FCB92A}"/>
+              <c16:uniqueId val="{00000000-C310-024F-8713-6E32B0B9A8B1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6261,7 +6335,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-7283-5249-A40E-10B6D9FCB92A}"/>
+              <c16:uniqueId val="{00000001-C310-024F-8713-6E32B0B9A8B1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6696,7 +6770,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E563-7E49-90FC-7F6CB370C452}"/>
+              <c16:uniqueId val="{00000000-F97E-1E4E-A763-3903DF5552F1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7027,7 +7101,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-E563-7E49-90FC-7F6CB370C452}"/>
+              <c16:uniqueId val="{00000001-F97E-1E4E-A763-3903DF5552F1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7222,7 +7296,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4A68-1E48-814E-94808C30C2B8}"/>
+              <c16:uniqueId val="{00000000-5CB9-5248-958F-E2E8EC92254E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7313,7 +7387,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-4A68-1E48-814E-94808C30C2B8}"/>
+              <c16:uniqueId val="{00000001-5CB9-5248-958F-E2E8EC92254E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7748,7 +7822,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-513B-F643-A976-3DD6E0422344}"/>
+              <c16:uniqueId val="{00000000-C68F-894B-923B-2419694B0830}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8079,7 +8153,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-513B-F643-A976-3DD6E0422344}"/>
+              <c16:uniqueId val="{00000001-C68F-894B-923B-2419694B0830}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8514,7 +8588,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-EE67-4C48-9521-6E5D3E0F14A6}"/>
+              <c16:uniqueId val="{00000000-D7C5-C340-AAED-EBF8B9913992}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8845,7 +8919,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-EE67-4C48-9521-6E5D3E0F14A6}"/>
+              <c16:uniqueId val="{00000001-D7C5-C340-AAED-EBF8B9913992}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9280,7 +9354,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8213-8344-A82A-3DBB53388AF1}"/>
+              <c16:uniqueId val="{00000000-F428-0A4E-83F6-BD72FDC90907}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9611,7 +9685,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-8213-8344-A82A-3DBB53388AF1}"/>
+              <c16:uniqueId val="{00000001-F428-0A4E-83F6-BD72FDC90907}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10046,7 +10120,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-CE6A-8241-84B5-8AF97ABB4B0F}"/>
+              <c16:uniqueId val="{00000000-2DC6-8A44-9659-C3A8F2CF92D9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10377,7 +10451,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-CE6A-8241-84B5-8AF97ABB4B0F}"/>
+              <c16:uniqueId val="{00000001-2DC6-8A44-9659-C3A8F2CF92D9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10472,6 +10546,2641 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart24.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>Baseline</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-GB" baseline="0"/>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>VGG: accuracy</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Train Acc (%)</c:v>
+          </c:tx>
+          <c:cat>
+            <c:numRef>
+              <c:f>Graphs!$A$5:$A$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Graphs!$B$5:$B$29</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>35.72</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>54.33</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>63.66</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>69.19</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>73.66</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>77.59</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>80.91</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>84.17</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>86.22</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>89.55</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>91.13</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>93.09</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>94.64</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>95.54</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>96.02</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>96.22</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>96.74</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>96.67</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>97.17</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>97.37</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>97.12</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>97.15</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>97.28</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>97.37</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DFCF-9144-AB61-19D2C9EDCAD0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Val Acc (%)</c:v>
+          </c:tx>
+          <c:cat>
+            <c:numRef>
+              <c:f>Graphs!$A$5:$A$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Graphs!$C$5:$C$29</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>48.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>59.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>66.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>68.2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>69.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>72.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>72.900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>74.400000000000006</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>75.7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>73.900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>74.8</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>74.400000000000006</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>73.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>74.900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>74.3</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>75.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>73.8</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>74.099999999999994</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>74.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>75.2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>73.8</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>73.8</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>73.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-DFCF-9144-AB61-19D2C9EDCAD0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:r>
+                  <a:rPr lang="en-GB"/>
+                  <a:t>Epoch</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48672768"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:r>
+                  <a:rPr lang="en-GB"/>
+                  <a:t>Accuracy (%)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48650112"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart25.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>Regularisation comparison: best validation accuracy</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Best Val Acc (%)</c:v>
+          </c:tx>
+          <c:invertIfNegative val="1"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Graphs!$A$35:$A$39</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Raw VGG</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Dropout</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Weight decay</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Augmentation</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Combined</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Graphs!$B$35:$B$39</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>85.3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>82.9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>88.4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>89.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-200D-354F-A6F3-7FCD16816102}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:r>
+                  <a:rPr lang="en-GB"/>
+                  <a:t>Model</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="675"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-SE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48672768"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:r>
+                  <a:rPr lang="en-GB"/>
+                  <a:t>Best validation accuracy (%)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48650112"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart26.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>Extension comparison: best validation accuracy</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Best Val Acc (%)</c:v>
+          </c:tx>
+          <c:invertIfNegative val="1"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Graphs!$A$46:$A$50</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Combined</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Advanced augmentation</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Learning-rate scheduler</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Downsampling</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Global average pooling</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Graphs!$B$46:$B$50</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>89.7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>90.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>88.8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>90.1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-217E-644F-AD9D-BD7B61FFFEC8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:r>
+                  <a:rPr lang="en-GB"/>
+                  <a:t>Model</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="675"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-SE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48672768"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:r>
+                  <a:rPr lang="en-GB"/>
+                  <a:t>Best validation accuracy (%)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48650112"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart27.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>Learning-rate scheduler:</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-GB" baseline="0"/>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>accuracy curve</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Train Acc (%)</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Graphs!$A$57:$A$106</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Graphs!$B$57:$B$106</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>40.71</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>55.82</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>63.3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>68.709999999999994</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>72.05</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>75.05</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>77.31</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>79.06</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>80.31</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>80.91</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>74.31</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>76.239999999999995</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>77.959999999999994</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>79.47</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>81.290000000000006</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>82.64</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>84.11</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>85.04</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>85.72</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>86.21</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>80.319999999999993</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>81.3</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>82.38</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>83.36</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>84.54</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>85.53</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>86.78</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>87.52</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>88.26</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>88.49</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>83.56</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>84.06</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>84.51</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>85.64</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>86.71</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>87.65</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>88.57</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>89.11</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>89.69</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>89.93</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>85.74</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>85.8</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>86.4</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>86.94</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>88.19</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>89.08</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>89.65</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>90.42</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>90.93</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>91.03</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5C2E-204B-BC92-DA8107527B37}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Val Acc (%)</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Graphs!$A$57:$A$106</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Graphs!$C$57:$C$106</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>61.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>71.7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>75.400000000000006</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>78.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>81.7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>83.3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>84.1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>83.7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>77.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>79.8</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>81.900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>82.2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>82.6</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>85.4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>85.6</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>86.6</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>86.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>86.9</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>83.2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>83.6</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>85.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>85.6</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>86.6</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>86.8</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>87.9</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>88.8</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>88.7</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>83.9</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>84.6</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>85.5</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>86.2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>89.6</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>88.7</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>89.1</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>88.7</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>89.3</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>86.9</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>86.6</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>86.6</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>86.5</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>87.6</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>90.2</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>90.4</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>89.9</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>90.1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5C2E-204B-BC92-DA8107527B37}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:r>
+                  <a:rPr lang="en-GB"/>
+                  <a:t>Epoch</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48672768"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:r>
+                  <a:rPr lang="en-GB"/>
+                  <a:t>Accuracy (%)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48650112"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart28.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>Learning-rate scheduler: loss curve</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Train Loss</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Graphs!$E$57:$E$106</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Graphs!$F$57:$F$106</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>1.6019000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.2332000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0458000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.90820000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.81040000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.73040000000000005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.66539999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.61370000000000002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.57920000000000005</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.56030000000000002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.75970000000000004</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.70189999999999997</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.65159999999999996</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.60750000000000004</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.55689999999999995</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.51490000000000002</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.47349999999999998</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.43980000000000002</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.41930000000000001</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.4088</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.58050000000000002</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.55940000000000001</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.5252</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.49249999999999999</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.45650000000000002</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.42430000000000001</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.38950000000000001</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.36899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.34350000000000003</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.33860000000000001</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.48720000000000002</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.47510000000000002</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.45440000000000003</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.42320000000000002</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.39479999999999998</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.36520000000000002</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.3357</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.3165</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.30170000000000002</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.29389999999999999</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.42130000000000001</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.42320000000000002</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.40100000000000002</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.37990000000000002</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.31950000000000001</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.30020000000000002</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.27710000000000001</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.26469999999999999</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.26029999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0B96-914F-9324-C7A488775F64}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Val Loss</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Graphs!$E$57:$E$106</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Graphs!$G$57:$G$106</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>1.3762000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1386000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.82089999999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.64459999999999995</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5746</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.52749999999999997</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.50039999999999996</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.4874</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.48139999999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.65210000000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.58430000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.53520000000000001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.49630000000000002</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.48870000000000002</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.43559999999999999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.40129999999999999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.3695</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.3674</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.36559999999999998</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.50149999999999995</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.48280000000000001</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.43890000000000001</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.43980000000000002</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.38500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.36609999999999998</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.35670000000000002</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.35930000000000001</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.34470000000000001</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.34200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.44979999999999998</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.4506</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.40860000000000002</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.38919999999999999</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.36059999999999998</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.34760000000000002</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.33479999999999999</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.33760000000000001</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.33679999999999999</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.33860000000000001</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.40350000000000003</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.35749999999999998</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.4254</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.39810000000000001</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.37409999999999999</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.32269999999999999</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.32619999999999999</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.30409999999999998</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.30830000000000002</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.30530000000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0B96-914F-9324-C7A488775F64}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:r>
+                  <a:rPr lang="en-GB"/>
+                  <a:t>Epoch</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48672768"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:r>
+                  <a:rPr lang="en-GB"/>
+                  <a:t>Loss</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48650112"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
@@ -10572,7 +13281,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-23AE-234D-A8FA-58B00D2BDA8F}"/>
+              <c16:uniqueId val="{00000000-AD41-7B46-9B7B-9F27F6BB3C0D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10663,7 +13372,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-23AE-234D-A8FA-58B00D2BDA8F}"/>
+              <c16:uniqueId val="{00000001-AD41-7B46-9B7B-9F27F6BB3C0D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10948,7 +13657,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-EA38-024D-A360-232BD12DD570}"/>
+              <c16:uniqueId val="{00000000-AB24-6844-828C-E93678B9D02E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11129,7 +13838,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-EA38-024D-A360-232BD12DD570}"/>
+              <c16:uniqueId val="{00000001-AB24-6844-828C-E93678B9D02E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11414,7 +14123,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-45A2-D242-8BB9-008706A1CDD7}"/>
+              <c16:uniqueId val="{00000000-CFFC-234C-9BA1-3AFE7CBE8515}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11595,7 +14304,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-45A2-D242-8BB9-008706A1CDD7}"/>
+              <c16:uniqueId val="{00000001-CFFC-234C-9BA1-3AFE7CBE8515}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11880,7 +14589,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2799-2542-B59F-313A71CC88DB}"/>
+              <c16:uniqueId val="{00000000-AE62-2546-AE32-E5829281950C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12061,7 +14770,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-2799-2542-B59F-313A71CC88DB}"/>
+              <c16:uniqueId val="{00000001-AE62-2546-AE32-E5829281950C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12346,7 +15055,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-481E-C54D-8E0C-5D7E87EE52B0}"/>
+              <c16:uniqueId val="{00000000-4B31-B54C-B39D-ECAD968C72D3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12527,7 +15236,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-481E-C54D-8E0C-5D7E87EE52B0}"/>
+              <c16:uniqueId val="{00000001-4B31-B54C-B39D-ECAD968C72D3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12812,7 +15521,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FCFB-1447-85FA-16318363EA30}"/>
+              <c16:uniqueId val="{00000000-9A82-C349-AD60-E6168B3759DB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12993,7 +15702,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-FCFB-1447-85FA-16318363EA30}"/>
+              <c16:uniqueId val="{00000001-9A82-C349-AD60-E6168B3759DB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -13278,7 +15987,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3646-0049-ADB4-DBF9F4CAB008}"/>
+              <c16:uniqueId val="{00000000-296D-5749-A0E6-BC5FE1566236}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -13459,7 +16168,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3646-0049-ADB4-DBF9F4CAB008}"/>
+              <c16:uniqueId val="{00000001-296D-5749-A0E6-BC5FE1566236}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -13818,6 +16527,191 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -14780,39 +17674,39 @@
     <col min="4" max="13" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="34.75" customHeight="1">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:13" ht="46.25" customHeight="1">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
@@ -15438,14 +18332,14 @@
     <col min="2" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="34.75" customHeight="1">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:5" ht="46.25" customHeight="1">
+      <c r="A1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
@@ -16363,14 +19257,14 @@
     <col min="2" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="34.75" customHeight="1">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:5" ht="46.25" customHeight="1">
+      <c r="A1" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
@@ -17288,14 +20182,14 @@
     <col min="2" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="34.75" customHeight="1">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:5" ht="46.25" customHeight="1">
+      <c r="A1" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
@@ -18213,14 +21107,14 @@
     <col min="2" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="34.75" customHeight="1">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:5" ht="46.25" customHeight="1">
+      <c r="A1" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
@@ -19126,6 +22020,1465 @@
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+  <dimension ref="A1:N106"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="5" max="14" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="21">
+      <c r="A1" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" s="10">
+        <v>35.72</v>
+      </c>
+      <c r="C5" s="10">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" s="10">
+        <v>54.33</v>
+      </c>
+      <c r="C6" s="10">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7" s="10">
+        <v>63.66</v>
+      </c>
+      <c r="C7" s="10">
+        <v>66.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8" s="10">
+        <v>69.19</v>
+      </c>
+      <c r="C8" s="10">
+        <v>68.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9" s="10">
+        <v>73.66</v>
+      </c>
+      <c r="C9" s="10">
+        <v>69.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10">
+        <v>6</v>
+      </c>
+      <c r="B10" s="10">
+        <v>77.59</v>
+      </c>
+      <c r="C10" s="10">
+        <v>72.599999999999994</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11">
+        <v>7</v>
+      </c>
+      <c r="B11" s="10">
+        <v>80.91</v>
+      </c>
+      <c r="C11" s="10">
+        <v>72.900000000000006</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12">
+        <v>8</v>
+      </c>
+      <c r="B12" s="10">
+        <v>84.17</v>
+      </c>
+      <c r="C12" s="10">
+        <v>74.400000000000006</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13">
+        <v>9</v>
+      </c>
+      <c r="B13" s="10">
+        <v>86.22</v>
+      </c>
+      <c r="C13" s="10">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14">
+        <v>10</v>
+      </c>
+      <c r="B14" s="10">
+        <v>89.55</v>
+      </c>
+      <c r="C14" s="10">
+        <v>75.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15">
+        <v>11</v>
+      </c>
+      <c r="B15" s="10">
+        <v>91.13</v>
+      </c>
+      <c r="C15" s="10">
+        <v>73.900000000000006</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16">
+        <v>12</v>
+      </c>
+      <c r="B16" s="10">
+        <v>93.09</v>
+      </c>
+      <c r="C16" s="10">
+        <v>74.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>13</v>
+      </c>
+      <c r="B17" s="10">
+        <v>94</v>
+      </c>
+      <c r="C17" s="10">
+        <v>74.400000000000006</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <v>14</v>
+      </c>
+      <c r="B18" s="10">
+        <v>94.64</v>
+      </c>
+      <c r="C18" s="10">
+        <v>73.599999999999994</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>15</v>
+      </c>
+      <c r="B19" s="10">
+        <v>95.54</v>
+      </c>
+      <c r="C19" s="10">
+        <v>74.900000000000006</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>16</v>
+      </c>
+      <c r="B20" s="10">
+        <v>96.02</v>
+      </c>
+      <c r="C20" s="10">
+        <v>74.3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <v>17</v>
+      </c>
+      <c r="B21" s="10">
+        <v>96.22</v>
+      </c>
+      <c r="C21" s="10">
+        <v>75.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <v>18</v>
+      </c>
+      <c r="B22" s="10">
+        <v>96.74</v>
+      </c>
+      <c r="C22" s="10">
+        <v>73.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>19</v>
+      </c>
+      <c r="B23" s="10">
+        <v>96.67</v>
+      </c>
+      <c r="C23" s="10">
+        <v>74.099999999999994</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
+        <v>20</v>
+      </c>
+      <c r="B24" s="10">
+        <v>97.17</v>
+      </c>
+      <c r="C24" s="10">
+        <v>74.599999999999994</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
+        <v>21</v>
+      </c>
+      <c r="B25" s="10">
+        <v>97.37</v>
+      </c>
+      <c r="C25" s="10">
+        <v>75.2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>22</v>
+      </c>
+      <c r="B26" s="10">
+        <v>97.12</v>
+      </c>
+      <c r="C26" s="10">
+        <v>73.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <v>23</v>
+      </c>
+      <c r="B27" s="10">
+        <v>97.15</v>
+      </c>
+      <c r="C27" s="10">
+        <v>73.8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28">
+        <v>24</v>
+      </c>
+      <c r="B28" s="10">
+        <v>97.28</v>
+      </c>
+      <c r="C28" s="10">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <v>25</v>
+      </c>
+      <c r="B29" s="10">
+        <v>97.37</v>
+      </c>
+      <c r="C29" s="10">
+        <v>73.7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35" s="10">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" s="10">
+        <v>85.3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" s="10">
+        <v>82.9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" s="10">
+        <v>88.4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>73</v>
+      </c>
+      <c r="B39" s="10">
+        <v>89.7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>73</v>
+      </c>
+      <c r="B46" s="10">
+        <v>89.7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>74</v>
+      </c>
+      <c r="B47" s="10">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>77</v>
+      </c>
+      <c r="B48" s="10">
+        <v>90.4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>75</v>
+      </c>
+      <c r="B49" s="10">
+        <v>88.8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>76</v>
+      </c>
+      <c r="B50" s="10">
+        <v>90.1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G56" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57">
+        <v>1</v>
+      </c>
+      <c r="B57" s="10">
+        <v>40.71</v>
+      </c>
+      <c r="C57" s="10">
+        <v>49</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
+      </c>
+      <c r="F57" s="10">
+        <v>1.6019000000000001</v>
+      </c>
+      <c r="G57" s="10">
+        <v>1.3762000000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58">
+        <v>2</v>
+      </c>
+      <c r="B58" s="10">
+        <v>55.82</v>
+      </c>
+      <c r="C58" s="10">
+        <v>61.2</v>
+      </c>
+      <c r="E58">
+        <v>2</v>
+      </c>
+      <c r="F58" s="10">
+        <v>1.2332000000000001</v>
+      </c>
+      <c r="G58" s="10">
+        <v>1.1386000000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59">
+        <v>3</v>
+      </c>
+      <c r="B59" s="10">
+        <v>63.3</v>
+      </c>
+      <c r="C59" s="10">
+        <v>71.7</v>
+      </c>
+      <c r="E59">
+        <v>3</v>
+      </c>
+      <c r="F59" s="10">
+        <v>1.0458000000000001</v>
+      </c>
+      <c r="G59" s="10">
+        <v>0.82089999999999996</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60">
+        <v>4</v>
+      </c>
+      <c r="B60" s="10">
+        <v>68.709999999999994</v>
+      </c>
+      <c r="C60" s="10">
+        <v>75.400000000000006</v>
+      </c>
+      <c r="E60">
+        <v>4</v>
+      </c>
+      <c r="F60" s="10">
+        <v>0.90820000000000001</v>
+      </c>
+      <c r="G60" s="10">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61">
+        <v>5</v>
+      </c>
+      <c r="B61" s="10">
+        <v>72.05</v>
+      </c>
+      <c r="C61" s="10">
+        <v>78.599999999999994</v>
+      </c>
+      <c r="E61">
+        <v>5</v>
+      </c>
+      <c r="F61" s="10">
+        <v>0.81040000000000001</v>
+      </c>
+      <c r="G61" s="10">
+        <v>0.64459999999999995</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62">
+        <v>6</v>
+      </c>
+      <c r="B62" s="10">
+        <v>75.05</v>
+      </c>
+      <c r="C62" s="10">
+        <v>80</v>
+      </c>
+      <c r="E62">
+        <v>6</v>
+      </c>
+      <c r="F62" s="10">
+        <v>0.73040000000000005</v>
+      </c>
+      <c r="G62" s="10">
+        <v>0.5746</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63">
+        <v>7</v>
+      </c>
+      <c r="B63" s="10">
+        <v>77.31</v>
+      </c>
+      <c r="C63" s="10">
+        <v>81.7</v>
+      </c>
+      <c r="E63">
+        <v>7</v>
+      </c>
+      <c r="F63" s="10">
+        <v>0.66539999999999999</v>
+      </c>
+      <c r="G63" s="10">
+        <v>0.52749999999999997</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64">
+        <v>8</v>
+      </c>
+      <c r="B64" s="10">
+        <v>79.06</v>
+      </c>
+      <c r="C64" s="10">
+        <v>83.3</v>
+      </c>
+      <c r="E64">
+        <v>8</v>
+      </c>
+      <c r="F64" s="10">
+        <v>0.61370000000000002</v>
+      </c>
+      <c r="G64" s="10">
+        <v>0.50039999999999996</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65">
+        <v>9</v>
+      </c>
+      <c r="B65" s="10">
+        <v>80.31</v>
+      </c>
+      <c r="C65" s="10">
+        <v>84.1</v>
+      </c>
+      <c r="E65">
+        <v>9</v>
+      </c>
+      <c r="F65" s="10">
+        <v>0.57920000000000005</v>
+      </c>
+      <c r="G65" s="10">
+        <v>0.4874</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66">
+        <v>10</v>
+      </c>
+      <c r="B66" s="10">
+        <v>80.91</v>
+      </c>
+      <c r="C66" s="10">
+        <v>83.7</v>
+      </c>
+      <c r="E66">
+        <v>10</v>
+      </c>
+      <c r="F66" s="10">
+        <v>0.56030000000000002</v>
+      </c>
+      <c r="G66" s="10">
+        <v>0.48139999999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67">
+        <v>11</v>
+      </c>
+      <c r="B67" s="10">
+        <v>74.31</v>
+      </c>
+      <c r="C67" s="10">
+        <v>77.599999999999994</v>
+      </c>
+      <c r="E67">
+        <v>11</v>
+      </c>
+      <c r="F67" s="10">
+        <v>0.75970000000000004</v>
+      </c>
+      <c r="G67" s="10">
+        <v>0.65210000000000001</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68">
+        <v>12</v>
+      </c>
+      <c r="B68" s="10">
+        <v>76.239999999999995</v>
+      </c>
+      <c r="C68" s="10">
+        <v>79.8</v>
+      </c>
+      <c r="E68">
+        <v>12</v>
+      </c>
+      <c r="F68" s="10">
+        <v>0.70189999999999997</v>
+      </c>
+      <c r="G68" s="10">
+        <v>0.58430000000000004</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69">
+        <v>13</v>
+      </c>
+      <c r="B69" s="10">
+        <v>77.959999999999994</v>
+      </c>
+      <c r="C69" s="10">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="E69">
+        <v>13</v>
+      </c>
+      <c r="F69" s="10">
+        <v>0.65159999999999996</v>
+      </c>
+      <c r="G69" s="10">
+        <v>0.53520000000000001</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70">
+        <v>14</v>
+      </c>
+      <c r="B70" s="10">
+        <v>79.47</v>
+      </c>
+      <c r="C70" s="10">
+        <v>82.2</v>
+      </c>
+      <c r="E70">
+        <v>14</v>
+      </c>
+      <c r="F70" s="10">
+        <v>0.60750000000000004</v>
+      </c>
+      <c r="G70" s="10">
+        <v>0.49630000000000002</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71">
+        <v>15</v>
+      </c>
+      <c r="B71" s="10">
+        <v>81.290000000000006</v>
+      </c>
+      <c r="C71" s="10">
+        <v>82.6</v>
+      </c>
+      <c r="E71">
+        <v>15</v>
+      </c>
+      <c r="F71" s="10">
+        <v>0.55689999999999995</v>
+      </c>
+      <c r="G71" s="10">
+        <v>0.48870000000000002</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72">
+        <v>16</v>
+      </c>
+      <c r="B72" s="10">
+        <v>82.64</v>
+      </c>
+      <c r="C72" s="10">
+        <v>85.4</v>
+      </c>
+      <c r="E72">
+        <v>16</v>
+      </c>
+      <c r="F72" s="10">
+        <v>0.51490000000000002</v>
+      </c>
+      <c r="G72" s="10">
+        <v>0.43559999999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73">
+        <v>17</v>
+      </c>
+      <c r="B73" s="10">
+        <v>84.11</v>
+      </c>
+      <c r="C73" s="10">
+        <v>85.6</v>
+      </c>
+      <c r="E73">
+        <v>17</v>
+      </c>
+      <c r="F73" s="10">
+        <v>0.47349999999999998</v>
+      </c>
+      <c r="G73" s="10">
+        <v>0.40129999999999999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74">
+        <v>18</v>
+      </c>
+      <c r="B74" s="10">
+        <v>85.04</v>
+      </c>
+      <c r="C74" s="10">
+        <v>86.6</v>
+      </c>
+      <c r="E74">
+        <v>18</v>
+      </c>
+      <c r="F74" s="10">
+        <v>0.43980000000000002</v>
+      </c>
+      <c r="G74" s="10">
+        <v>0.3695</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75">
+        <v>19</v>
+      </c>
+      <c r="B75" s="10">
+        <v>85.72</v>
+      </c>
+      <c r="C75" s="10">
+        <v>86.5</v>
+      </c>
+      <c r="E75">
+        <v>19</v>
+      </c>
+      <c r="F75" s="10">
+        <v>0.41930000000000001</v>
+      </c>
+      <c r="G75" s="10">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76">
+        <v>20</v>
+      </c>
+      <c r="B76" s="10">
+        <v>86.21</v>
+      </c>
+      <c r="C76" s="10">
+        <v>86.9</v>
+      </c>
+      <c r="E76">
+        <v>20</v>
+      </c>
+      <c r="F76" s="10">
+        <v>0.4088</v>
+      </c>
+      <c r="G76" s="10">
+        <v>0.36559999999999998</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77">
+        <v>21</v>
+      </c>
+      <c r="B77" s="10">
+        <v>80.319999999999993</v>
+      </c>
+      <c r="C77" s="10">
+        <v>83.2</v>
+      </c>
+      <c r="E77">
+        <v>21</v>
+      </c>
+      <c r="F77" s="10">
+        <v>0.58050000000000002</v>
+      </c>
+      <c r="G77" s="10">
+        <v>0.50149999999999995</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78">
+        <v>22</v>
+      </c>
+      <c r="B78" s="10">
+        <v>81.3</v>
+      </c>
+      <c r="C78" s="10">
+        <v>83.6</v>
+      </c>
+      <c r="E78">
+        <v>22</v>
+      </c>
+      <c r="F78" s="10">
+        <v>0.55940000000000001</v>
+      </c>
+      <c r="G78" s="10">
+        <v>0.48280000000000001</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79">
+        <v>23</v>
+      </c>
+      <c r="B79" s="10">
+        <v>82.38</v>
+      </c>
+      <c r="C79" s="10">
+        <v>85.5</v>
+      </c>
+      <c r="E79">
+        <v>23</v>
+      </c>
+      <c r="F79" s="10">
+        <v>0.5252</v>
+      </c>
+      <c r="G79" s="10">
+        <v>0.43890000000000001</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80">
+        <v>24</v>
+      </c>
+      <c r="B80" s="10">
+        <v>83.36</v>
+      </c>
+      <c r="C80" s="10">
+        <v>85.6</v>
+      </c>
+      <c r="E80">
+        <v>24</v>
+      </c>
+      <c r="F80" s="10">
+        <v>0.49249999999999999</v>
+      </c>
+      <c r="G80" s="10">
+        <v>0.43980000000000002</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81">
+        <v>25</v>
+      </c>
+      <c r="B81" s="10">
+        <v>84.54</v>
+      </c>
+      <c r="C81" s="10">
+        <v>86.6</v>
+      </c>
+      <c r="E81">
+        <v>25</v>
+      </c>
+      <c r="F81" s="10">
+        <v>0.45650000000000002</v>
+      </c>
+      <c r="G81" s="10">
+        <v>0.38500000000000001</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82">
+        <v>26</v>
+      </c>
+      <c r="B82" s="10">
+        <v>85.53</v>
+      </c>
+      <c r="C82" s="10">
+        <v>86.8</v>
+      </c>
+      <c r="E82">
+        <v>26</v>
+      </c>
+      <c r="F82" s="10">
+        <v>0.42430000000000001</v>
+      </c>
+      <c r="G82" s="10">
+        <v>0.36609999999999998</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83">
+        <v>27</v>
+      </c>
+      <c r="B83" s="10">
+        <v>86.78</v>
+      </c>
+      <c r="C83" s="10">
+        <v>87.9</v>
+      </c>
+      <c r="E83">
+        <v>27</v>
+      </c>
+      <c r="F83" s="10">
+        <v>0.38950000000000001</v>
+      </c>
+      <c r="G83" s="10">
+        <v>0.35670000000000002</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84">
+        <v>28</v>
+      </c>
+      <c r="B84" s="10">
+        <v>87.52</v>
+      </c>
+      <c r="C84" s="10">
+        <v>88</v>
+      </c>
+      <c r="E84">
+        <v>28</v>
+      </c>
+      <c r="F84" s="10">
+        <v>0.36899999999999999</v>
+      </c>
+      <c r="G84" s="10">
+        <v>0.35930000000000001</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85">
+        <v>29</v>
+      </c>
+      <c r="B85" s="10">
+        <v>88.26</v>
+      </c>
+      <c r="C85" s="10">
+        <v>88.8</v>
+      </c>
+      <c r="E85">
+        <v>29</v>
+      </c>
+      <c r="F85" s="10">
+        <v>0.34350000000000003</v>
+      </c>
+      <c r="G85" s="10">
+        <v>0.34470000000000001</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86">
+        <v>30</v>
+      </c>
+      <c r="B86" s="10">
+        <v>88.49</v>
+      </c>
+      <c r="C86" s="10">
+        <v>88.7</v>
+      </c>
+      <c r="E86">
+        <v>30</v>
+      </c>
+      <c r="F86" s="10">
+        <v>0.33860000000000001</v>
+      </c>
+      <c r="G86" s="10">
+        <v>0.34200000000000003</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87">
+        <v>31</v>
+      </c>
+      <c r="B87" s="10">
+        <v>83.56</v>
+      </c>
+      <c r="C87" s="10">
+        <v>83.9</v>
+      </c>
+      <c r="E87">
+        <v>31</v>
+      </c>
+      <c r="F87" s="10">
+        <v>0.48720000000000002</v>
+      </c>
+      <c r="G87" s="10">
+        <v>0.44979999999999998</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88">
+        <v>32</v>
+      </c>
+      <c r="B88" s="10">
+        <v>84.06</v>
+      </c>
+      <c r="C88" s="10">
+        <v>84.6</v>
+      </c>
+      <c r="E88">
+        <v>32</v>
+      </c>
+      <c r="F88" s="10">
+        <v>0.47510000000000002</v>
+      </c>
+      <c r="G88" s="10">
+        <v>0.4506</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89">
+        <v>33</v>
+      </c>
+      <c r="B89" s="10">
+        <v>84.51</v>
+      </c>
+      <c r="C89" s="10">
+        <v>85.5</v>
+      </c>
+      <c r="E89">
+        <v>33</v>
+      </c>
+      <c r="F89" s="10">
+        <v>0.45440000000000003</v>
+      </c>
+      <c r="G89" s="10">
+        <v>0.40860000000000002</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90">
+        <v>34</v>
+      </c>
+      <c r="B90" s="10">
+        <v>85.64</v>
+      </c>
+      <c r="C90" s="10">
+        <v>86.2</v>
+      </c>
+      <c r="E90">
+        <v>34</v>
+      </c>
+      <c r="F90" s="10">
+        <v>0.42320000000000002</v>
+      </c>
+      <c r="G90" s="10">
+        <v>0.38919999999999999</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91">
+        <v>35</v>
+      </c>
+      <c r="B91" s="10">
+        <v>86.71</v>
+      </c>
+      <c r="C91" s="10">
+        <v>88</v>
+      </c>
+      <c r="E91">
+        <v>35</v>
+      </c>
+      <c r="F91" s="10">
+        <v>0.39479999999999998</v>
+      </c>
+      <c r="G91" s="10">
+        <v>0.36059999999999998</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92">
+        <v>36</v>
+      </c>
+      <c r="B92" s="10">
+        <v>87.65</v>
+      </c>
+      <c r="C92" s="10">
+        <v>89.6</v>
+      </c>
+      <c r="E92">
+        <v>36</v>
+      </c>
+      <c r="F92" s="10">
+        <v>0.36520000000000002</v>
+      </c>
+      <c r="G92" s="10">
+        <v>0.34760000000000002</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93">
+        <v>37</v>
+      </c>
+      <c r="B93" s="10">
+        <v>88.57</v>
+      </c>
+      <c r="C93" s="10">
+        <v>88.7</v>
+      </c>
+      <c r="E93">
+        <v>37</v>
+      </c>
+      <c r="F93" s="10">
+        <v>0.3357</v>
+      </c>
+      <c r="G93" s="10">
+        <v>0.33479999999999999</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94">
+        <v>38</v>
+      </c>
+      <c r="B94" s="10">
+        <v>89.11</v>
+      </c>
+      <c r="C94" s="10">
+        <v>89.1</v>
+      </c>
+      <c r="E94">
+        <v>38</v>
+      </c>
+      <c r="F94" s="10">
+        <v>0.3165</v>
+      </c>
+      <c r="G94" s="10">
+        <v>0.33760000000000001</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95">
+        <v>39</v>
+      </c>
+      <c r="B95" s="10">
+        <v>89.69</v>
+      </c>
+      <c r="C95" s="10">
+        <v>88.7</v>
+      </c>
+      <c r="E95">
+        <v>39</v>
+      </c>
+      <c r="F95" s="10">
+        <v>0.30170000000000002</v>
+      </c>
+      <c r="G95" s="10">
+        <v>0.33679999999999999</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96">
+        <v>40</v>
+      </c>
+      <c r="B96" s="10">
+        <v>89.93</v>
+      </c>
+      <c r="C96" s="10">
+        <v>89.3</v>
+      </c>
+      <c r="E96">
+        <v>40</v>
+      </c>
+      <c r="F96" s="10">
+        <v>0.29389999999999999</v>
+      </c>
+      <c r="G96" s="10">
+        <v>0.33860000000000001</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97">
+        <v>41</v>
+      </c>
+      <c r="B97" s="10">
+        <v>85.74</v>
+      </c>
+      <c r="C97" s="10">
+        <v>86.9</v>
+      </c>
+      <c r="E97">
+        <v>41</v>
+      </c>
+      <c r="F97" s="10">
+        <v>0.42130000000000001</v>
+      </c>
+      <c r="G97" s="10">
+        <v>0.40350000000000003</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98">
+        <v>42</v>
+      </c>
+      <c r="B98" s="10">
+        <v>85.8</v>
+      </c>
+      <c r="C98" s="10">
+        <v>86.6</v>
+      </c>
+      <c r="E98">
+        <v>42</v>
+      </c>
+      <c r="F98" s="10">
+        <v>0.42320000000000002</v>
+      </c>
+      <c r="G98" s="10">
+        <v>0.35749999999999998</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99">
+        <v>43</v>
+      </c>
+      <c r="B99" s="10">
+        <v>86.4</v>
+      </c>
+      <c r="C99" s="10">
+        <v>86.6</v>
+      </c>
+      <c r="E99">
+        <v>43</v>
+      </c>
+      <c r="F99" s="10">
+        <v>0.40100000000000002</v>
+      </c>
+      <c r="G99" s="10">
+        <v>0.4254</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100">
+        <v>44</v>
+      </c>
+      <c r="B100" s="10">
+        <v>86.94</v>
+      </c>
+      <c r="C100" s="10">
+        <v>86.5</v>
+      </c>
+      <c r="E100">
+        <v>44</v>
+      </c>
+      <c r="F100" s="10">
+        <v>0.37990000000000002</v>
+      </c>
+      <c r="G100" s="10">
+        <v>0.39810000000000001</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101">
+        <v>45</v>
+      </c>
+      <c r="B101" s="10">
+        <v>88.19</v>
+      </c>
+      <c r="C101" s="10">
+        <v>87.6</v>
+      </c>
+      <c r="E101">
+        <v>45</v>
+      </c>
+      <c r="F101" s="10">
+        <v>0.35</v>
+      </c>
+      <c r="G101" s="10">
+        <v>0.37409999999999999</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102">
+        <v>46</v>
+      </c>
+      <c r="B102" s="10">
+        <v>89.08</v>
+      </c>
+      <c r="C102" s="10">
+        <v>89</v>
+      </c>
+      <c r="E102">
+        <v>46</v>
+      </c>
+      <c r="F102" s="10">
+        <v>0.31950000000000001</v>
+      </c>
+      <c r="G102" s="10">
+        <v>0.32269999999999999</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103">
+        <v>47</v>
+      </c>
+      <c r="B103" s="10">
+        <v>89.65</v>
+      </c>
+      <c r="C103" s="10">
+        <v>90.2</v>
+      </c>
+      <c r="E103">
+        <v>47</v>
+      </c>
+      <c r="F103" s="10">
+        <v>0.30020000000000002</v>
+      </c>
+      <c r="G103" s="10">
+        <v>0.32619999999999999</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104">
+        <v>48</v>
+      </c>
+      <c r="B104" s="10">
+        <v>90.42</v>
+      </c>
+      <c r="C104" s="10">
+        <v>90.4</v>
+      </c>
+      <c r="E104">
+        <v>48</v>
+      </c>
+      <c r="F104" s="10">
+        <v>0.27710000000000001</v>
+      </c>
+      <c r="G104" s="10">
+        <v>0.30409999999999998</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105">
+        <v>49</v>
+      </c>
+      <c r="B105" s="10">
+        <v>90.93</v>
+      </c>
+      <c r="C105" s="10">
+        <v>89.9</v>
+      </c>
+      <c r="E105">
+        <v>49</v>
+      </c>
+      <c r="F105" s="10">
+        <v>0.26469999999999999</v>
+      </c>
+      <c r="G105" s="10">
+        <v>0.30830000000000002</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106">
+        <v>50</v>
+      </c>
+      <c r="B106" s="10">
+        <v>91.03</v>
+      </c>
+      <c r="C106" s="10">
+        <v>90.1</v>
+      </c>
+      <c r="E106">
+        <v>50</v>
+      </c>
+      <c r="F106" s="10">
+        <v>0.26029999999999998</v>
+      </c>
+      <c r="G106" s="10">
+        <v>0.30530000000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -19144,17 +23497,17 @@
     <col min="8" max="8" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="34.75" customHeight="1">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:8" ht="46.25" customHeight="1">
+      <c r="A1" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
@@ -29212,14 +33565,14 @@
     <col min="2" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="34.75" customHeight="1">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:5" ht="46.25" customHeight="1">
+      <c r="A1" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
@@ -29457,14 +33810,14 @@
     <col min="2" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="34.75" customHeight="1">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:5" ht="46.25" customHeight="1">
+      <c r="A1" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
@@ -29957,14 +34310,14 @@
     <col min="2" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="34.75" customHeight="1">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:5" ht="46.25" customHeight="1">
+      <c r="A1" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
@@ -30457,14 +34810,14 @@
     <col min="2" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="34.75" customHeight="1">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:5" ht="46.25" customHeight="1">
+      <c r="A1" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
@@ -30957,14 +35310,14 @@
     <col min="2" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="34.75" customHeight="1">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:5" ht="46.25" customHeight="1">
+      <c r="A1" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
@@ -31457,14 +35810,14 @@
     <col min="2" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="34.75" customHeight="1">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:5" ht="46.25" customHeight="1">
+      <c r="A1" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
@@ -31957,14 +36310,14 @@
     <col min="2" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="34.75" customHeight="1">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:5" ht="46.25" customHeight="1">
+      <c r="A1" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
